--- a/artfynd/A 37283-2023 artfynd.xlsx
+++ b/artfynd/A 37283-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 37283-2023 artfynd.xlsx
+++ b/artfynd/A 37283-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113418140</v>
+        <v>131674679</v>
       </c>
       <c r="B2" t="n">
-        <v>57281</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92596</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,31 +686,26 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>1106</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vågticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Osteina undosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Peck) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -723,13 +713,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>562649</v>
+        <v>562635</v>
       </c>
       <c r="R2" t="n">
-        <v>6464566</v>
+        <v>6464544</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -753,17 +743,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-11-26</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-11-26</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Hanen som brukar hålla till här i reservatsförslaget och en hona</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -772,6 +757,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -787,6 +773,519 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>92457467</v>
+      </c>
+      <c r="B3" t="n">
+        <v>91909</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Åtvidaberg, Ög</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>562633</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6464540</v>
+      </c>
+      <c r="S3" t="n">
+        <v>25</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Björsäter</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2021-04-16</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2021-04-16</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Jens Johannesson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Jens Johannesson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>113418141</v>
+      </c>
+      <c r="B4" t="n">
+        <v>91909</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Risten , Ög</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>562634</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6464540</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Björsäter</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2023-11-26</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2023-11-26</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>68602097</v>
+      </c>
+      <c r="B5" t="n">
+        <v>92143</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>1618</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Hängticka</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Postia ceriflua</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Berk. &amp; M.A.Curtis) Jülich</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Byrumsskogen, Ög</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>562656</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6464600</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Björsäter</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2017-11-17</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2017-12-07</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>113418140</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Risten , Ög</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>562649</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6464566</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Björsäter</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2023-11-26</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2023-11-26</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Hanen som brukar hålla till här i reservatsförslaget och en hona</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>113248991</v>
+      </c>
+      <c r="B7" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Risten , Ög</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>562631</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6464571</v>
+      </c>
+      <c r="S7" t="n">
+        <v>1</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Björsäter</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2023-11-11</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2023-11-11</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Inne I av Södra planerad avverkningsanmälan A37222-23.  Skoglig värdekärna V1 klassad av Länsstyrelsen.</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 37283-2023 artfynd.xlsx
+++ b/artfynd/A 37283-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131674679</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -871,6 +881,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92457467</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -972,6 +987,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113418141</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1069,6 +1089,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/68602097</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1179,6 +1204,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113418140</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1286,8 +1316,21 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113248991</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>